--- a/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.3).xlsx
+++ b/Hardware/Controller/JLC_PCBA_BOM-DALI_EVG_Controller(V0.3).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="141">
   <si>
     <t xml:space="preserve">Comment</t>
   </si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">C21</t>
   </si>
   <si>
-    <t xml:space="preserve">220uF/50V</t>
+    <t xml:space="preserve">220uF/35V</t>
   </si>
   <si>
     <t xml:space="preserve">Polarized Capacitor (Axial)</t>
@@ -373,6 +373,9 @@
     <t xml:space="preserve">C2488</t>
   </si>
   <si>
+    <t xml:space="preserve">C99561</t>
+  </si>
+  <si>
     <t xml:space="preserve">C1002</t>
   </si>
   <si>
@@ -382,9 +385,15 @@
     <t xml:space="preserve">C262659</t>
   </si>
   <si>
+    <t xml:space="preserve">C474881</t>
+  </si>
+  <si>
     <t xml:space="preserve">C1051</t>
   </si>
   <si>
+    <t xml:space="preserve">C441171</t>
+  </si>
+  <si>
     <t xml:space="preserve">C20917</t>
   </si>
   <si>
@@ -433,16 +442,7 @@
     <t xml:space="preserve">C6482</t>
   </si>
   <si>
-    <t xml:space="preserve">C44705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C99561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C441171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C474881</t>
+    <t xml:space="preserve">C1590097</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -952,7 +952,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -972,7 +972,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1052,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1072,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1189,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1229,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1249,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1269,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1289,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1329,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1369,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1389,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
